--- a/data/users.xlsx
+++ b/data/users.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27B78429-B7A1-4A3F-9AAB-224EC57F8BB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="1" r:id="rId1"/>

--- a/data/users.xlsx
+++ b/data/users.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shah.newaj\PycharmProjects\Cash-Voucher-Activities-CVA-\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27B78429-B7A1-4A3F-9AAB-224EC57F8BB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98A8DBF4-FF0E-496A-81D0-94A08CC2177D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="61">
   <si>
     <t>full_name</t>
   </si>
@@ -939,20 +939,44 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
+      <c r="A3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
+      <c r="A4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -1013,6 +1037,8 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" display="mailto:newaj01@gmail.com" xr:uid="{8EDE8068-9149-4012-AE05-7DC2FE5CDEDB}"/>
+    <hyperlink ref="C3" r:id="rId2" display="mailto:karim02@gmail.com" xr:uid="{207F8C3B-073C-48D1-ACAE-4D5C88910B19}"/>
+    <hyperlink ref="C4" r:id="rId3" xr:uid="{DAB45A8D-FD82-4488-B4C5-B7462169C4F6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
